--- a/data/data_replicated/4p_nomod_sFRiman/traces_references.xlsx
+++ b/data/data_replicated/4p_nomod_sFRiman/traces_references.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">trace</t>
   </si>
@@ -20,7 +20,7 @@
     <t xml:space="preserve">reference</t>
   </si>
   <si>
-    <t xml:space="preserve">c29-c31-c50-c30-29d2d-31d2U15-50d2d-30d2c-05-05-025-05-29622-29698-34331-40392.csv</t>
+    <t xml:space="preserve">c29-c31-c50-c30-29d3a-31d3a-50d4a-30d3a-00625-003125-003125-0125-9973-11425-14364-28624.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c29</t>
@@ -35,19 +35,22 @@
     <t xml:space="preserve">c50</t>
   </si>
   <si>
-    <t xml:space="preserve">c29-c31-c50-c30-29d3a-31d3a-50d4a-30d3a-00625-003125-003125-0125-9973-11425-14364-28624.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c31-c50-c30-29d3e-31d3U60-50d4c-30d3c-016-0125-003125-0125-5978-6283-6468-12116.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c50-c31-c30-29d2c-50d3c-31d2-30d2c-025-00625-30-05-17362-17497-18166-40392.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c50-c31-c30-29d3d-50d4e-31d3U15-30d3e-003125-003-00625-014-2539-2631-2770-4896.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c50-c31-c30-29d3e-50d4c-31d2-30d3d-003125-00078-45-00625-2230-2271-2278-3798.csv</t>
+    <t xml:space="preserve">c29-c50-c31-c30-29d3d-50d4e-31d3a-30d3e-003125-003-00078-014-2539-2631-3494-4896.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c29-c50-c31-c30-29d3e-50d4c-31d3a-30d3c-016-003125-00156-0125-5978-6468-6584-12116.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c29-c50-c31-c30-29d3e-50d4c-31d3a-30d3d-003125-00078-00078-00625-2230-2271-3494-3798.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c31-c29-c50-c30-31d3a-29d2c-50d3c-30d2c-003125-025-00625-05-11425-17362-17497-40392.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c31-c29-c50-c30-31d3a-29d2d-50d2d-30d2c-00625-05-025-05-29248-29622-34331-40392.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c31-c50-c29-c30-31d3a-50d3e-29d2e-30d2d-003125-025-025-05-11425-14225-15935-27775.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c31-c50-c29-c30-31d3a-50d4a-29d2a-30d2a-0125-016-025-05-52403-67760-72765-142279.csv</t>
@@ -56,10 +59,10 @@
     <t xml:space="preserve">c31-c50-c29-c30-31d3a-50d4a-29d3a-30d2a-00625-00625-0125-025-29248-31136-37375-64015.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c31-c50-c29-c30-31d4I35-50d4c-29d3d-30d2d-003125-005-027-025-7632-7994-9048-14610.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c33-c35-c34-32d4I15-33d2e-35d4I35-34d1e-003125-00625-00625-05-14272-14908-16125-172745.csv</t>
+    <t xml:space="preserve">c31-c50-c29-c30-31d3a-50d4c-29d3d-30d2d-00156-005-027-025-6584-7994-9048-14610.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c32-c35-c33-c34-32d3a-35d3a-33d2d-34d1e-003125-003125-00625-05-10650-12329-16805-172745.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c32</t>
@@ -74,70 +77,67 @@
     <t xml:space="preserve">c35</t>
   </si>
   <si>
+    <t xml:space="preserve">c32-c35-c33-c34-32d3a-35d3a-33d2e-34d1d-00625-00625-0125-05-31167-31784-32427-256927.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c32-c35-c33-c34-32d3a-35d3a-33d2e-34d1e-003125-003125-00625-05-10650-12329-14908-172745.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c32-c35-c33-c34-32d3a-35d3a-33d2e-34d2c-003125-003125-00625-025-10650-12329-14908-85903.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c32-c35-c33-c34-32d3a-35d3a-33d4a-34d2a-003125-003125-003125-025-10650-12329-15979-194058.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c33-c32-c35-c34-33d2d-32d3a-35d3a-34d1c-00625-00625-00625-05-16805-31167-31784-236603.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c33-c32-c35-c34-33d4a-32d3a-35d3a-34d2a-003125-00625-00625-025-15979-31167-31784-194058.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c33-c32-c35-c34-33d4a-32d3a-35d3a-34d2a-003125-00625-00625-05-15979-31167-31784-312081.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c33-c32-c35-c34-33d4c-32d2-35d3S30-34d2e-002-30-009-0125-4709-6327-6600-55121.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c35-c32-c34-33d2d-35d2-32d2-34d1c-00625-15-45-05-16805-23396-23497-236603.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c35-c32-c34-33d2d-35d3I22-32d2S30-34d1e-00625-00625-0125-05-16805-17021-18835-172745.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c35-c32-c34-33d2e-35d4I35-32d3S30-34d2c-003125-003125-009-025-8011-8839-9643-85903.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c35-c32-c34-33d3d-35d1-32d3U60-34d2c-00156-45-00313-00625-4173-4553-4812-36985.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c35-c32-c34-33d4c-35d4I35-32d4I35-34d2d-002-00156-00156-0125-4709-5192-5564-48089.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c36-c34-c35-33d2d-36d3I15-34d2c-35d1-00625-00625-025-15-16805-22279-85903-88038.csv</t>
+    <t xml:space="preserve">c33-c35-c32-c34-33d4c-35d3a-32d3a-34d2d-002-00156-00156-0125-4709-5558-6213-48089.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c33-c35-c32-c34-33d4c-35d3a-32d3a-34d2e-002-00156-00156-0125-4709-5558-6213-55121.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c33-c36-c34-c35-33d2d-36d3a-34d2c-35d2a-00625-0125-025-025-16805-22142-85903-98921.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c36</t>
   </si>
   <si>
-    <t xml:space="preserve">c33-c36-c34-c35-33d3d-36d2-34d3c-35d3I22-00156-45-003125-00625-4173-4386-14703-17021.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c33-c36-c34-c35-33d4a-36d3a-34d2a-35d3a-003125-0125-0125-036-15979-22142-80087-145466.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c33-c36-c34-c35-33d4c-36d3S2-34d3d-35d2-00078-00078-003125-30-2507-2688-9276-9957.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c36-c35-c34-33d3e-36d3-35d4I22-34d3e-00078-15-003125-003125-1723-1930-8529-9252.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c33-c36-c35-c34-33d4c-36d3-35d2-34d2d-002-15-15-00625-4709-6057-23396-25565.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c32-c33-c34-35d1S30-32d3-33d2e-34d1d-025-30-0125-05-27091-30221-32427-256927.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c32-c33-c34-35d2S30-32d3-33d2e-34d2c-0125-30-00625-025-12898-13667-14908-85903.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c32-c33-c34-35d2S30-32d4I15-33d2e-34d2c-0125-003125-00625-025-12898-14272-14908-85903.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c32-c33-c34-35d3-32d4I22-33d2e-34d2e-30-00156-003125-025-7217-7266-8011-69480.csv</t>
+    <t xml:space="preserve">c33-c36-c34-c35-33d4c-36d3a-34d2d-35d3a-002-00625-00625-00625-4709-8275-25565-31784.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c33-c36-c34-c35-33d4c-36d3a-34d3d-35d3a-00078-003125-003125-003125-2507-2719-9276-12329.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c33-c36-c35-c34-33d3e-36d3a-35d3a-34d3e-00078-00156-00156-003125-1723-1860-5558-9252.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c32-c33-c34-35d3a-32d3a-33d2e-34d2e-00156-00156-003125-025-5558-6213-8011-69480.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c35-c32-c33-c34-35d3a-32d3a-33d4a-34d2a-00156-00156-00156-0125-5558-6213-9610-80087.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c33-c34-c35-36d2-33d3d-34d2c-35d3-30-003125-00625-15-9316-10112-36985-37986.csv</t>
+    <t xml:space="preserve">c35-c33-c32-c34-35d3a-33d2e-32d3a-34d2c-00156-003125-003125-025-5558-8011-10650-85903.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c33-c32-c34-35d3a-33d3d-32d3a-34d2c-00078-00156-00078-00625-2745-4173-4326-36985.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c33-c34-c35-36d3a-33d2e-34d2e-35d3a-00625-00625-0125-0125-8275-14908-55121-64102.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c33-c34-c35-36d3a-33d3e-34d2d-35d3a-00625-01-0125-0125-8275-11524-48089-64102.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c36-c33-c34-c35-36d3a-33d4a-34d3a-35d3a-00625-003125-00625-0125-8275-15979-47748-64102.csv</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">c36-c33-c34-c35-36d3a-33d4a-34d4a-35d3a-00625-00156-005-00625-8275-9610-28046-31784.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c33-c34-c35-36d4I15-33d3e-34d2d-35d3I15-003125-01-0125-025-11311-11524-48089-58375.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c33-c34-c35-36d4I22-33d2e-34d2e-35d3I15-00625-00625-0125-025-14204-14908-55121-58375.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c33-c35-c34-36d3-33d3e-35d2S30-34d3c-15-00156-0125-003125-2871-2969-12898-14703.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c39-c37-c38-36d3-39d3S2-37d4I15-38d2S30-15-00156-00156-00625-2871-3643-6143-6181.csv</t>
+    <t xml:space="preserve">c36-c33-c35-c34-36d3a-33d3d-35d3a-34d2c-00625-003125-00625-00625-8275-10112-31784-36985.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c33-c35-c34-36d3a-33d3d-35d3a-34d3c-003125-00156-003125-003125-2719-4173-12329-14703.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c33-c35-c34-36d3a-33d3e-35d3a-34d3c-003125-00156-003125-003125-2719-2969-12329-14703.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c38-c39-c37-36d3a-38d3a-39d3a-37d3a-00078-00078-00078-00078-1251-2135-2522-2793.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c37</t>
@@ -167,6 +167,9 @@
     <t xml:space="preserve">c39</t>
   </si>
   <si>
+    <t xml:space="preserve">c36-c38-c39-c37-36d3a-38d3a-39d3a-37d3a-00156-00078-00078-00078-1860-2135-2522-2793.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c36-c39-c37-c38-36d3S2-39d3S2-37d2S10-38d1S30-003125-003125-0125-025-7377-8431-28808-32660.csv</t>
   </si>
   <si>
@@ -176,42 +179,39 @@
     <t xml:space="preserve">c36-c39-c37-c38-36d3S2-39d3S2-37d3S10-38d3S30-00078-00156-003125-007-2688-3643-5632-6155.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c39-c37-c38-36d4I22-39d4I35-37d4I22-38d4I35-003125-003125-00625-00625-8409-8459-17284-17524.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c36-c39-c38-c37-36d3a-39d3a-38d2a-37d2a-0125-00625-025-025-22142-33341-66892-68907.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c37-c40-c38-c39-37d3-40d3-38d3-39d2-45-30-15-15-2046-2172-19523-19843.csv</t>
+    <t xml:space="preserve">c36-c39-c38-c37-36d3a-39d3a-38d3a-37d3a-003125-00156-003125-003125-2719-6855-7130-8324.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c39-c38-c37-36d3a-39d3a-38d3a-37d3a-00625-003125-0125-0125-8275-11974-27797-31376.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c37-c40-c38-c39-37d3a-40d3a-38d2a-39d3a-00156-00156-025-0125-5376-6419-66892-67994.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c40</t>
   </si>
   <si>
-    <t xml:space="preserve">c37-c40-c38-c39-37d4I15-40d2-38d1S30-39d3I15-00156-45-05-0125-6143-6498-54628-60529.csv</t>
+    <t xml:space="preserve">c37-c40-c38-c39-37d3a-40d3a-38d3a-39d3a-00078-00078-0125-00625-2793-3898-27797-33341.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c37-c40-c39-c38-37d3a-40d3a-39d3a-38d2a-003125-003125-025-05-8324-14282-112158-130968.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c37-c40-c39-c38-37d4I15-40d2-39d3I15-38d3I35-00156-45-0125-025-6143-6498-60529-62127.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c36-c37-c38-39d4I15-36d4I35-37d2S10-38d3I35-003125-00625-0125-0125-14869-15874-28808-29794.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c36-c38-c37-39d2-36d2-38d2-37d2-45-45-45-30-634-746-1761-1804.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c36-c38-c37-39d2-36d2-38d3S30-37d1-45-45-003125-30-1501-1604-3045-3070.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c36-c38-c37-39d2-36d3S2-38d4I15-37d1-30-00078-00156-45-2498-2688-4847-4982.csv</t>
+    <t xml:space="preserve">c37-c40-c39-c38-37d3a-40d3a-39d3a-38d3a-00078-00078-003125-00625-2793-3898-11974-15325.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c39-c36-c37-c38-39d3a-36d3a-37d3a-38d3a-00078-003125-00156-003125-2522-2719-5376-7130.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c39-c36-c38-c37-39d3S2-36d3S2-38d3S30-37d3S10-00078-00078-003125-00156-1765-2688-3045-3702.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c39-c36-c38-c37-39d3a-36d3a-38d3a-37d3a-00078-003125-00156-00156-2522-2719-4218-5376.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c39-c36-c38-c37-39d3a-36d3a-38d3a-37d3a-00078-003125-003125-003125-2522-2719-7130-8324.csv</t>
   </si>
   <si>
@@ -221,69 +221,36 @@
     <t xml:space="preserve">c39-c36-c38-c37-39d3a-36d3a-38d3a-37d3a-003125-0125-0125-0125-11974-22142-27797-31376.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c39-c36-c38-c37-39d4I35-36d1-38d2-37d4I15-00156-45-15-003125-4825-5296-10893-11726.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c36-c38-c37-39d4I35-36d2-38d1-37d1-003125-30-30-30-8459-9316-17779-18618.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c37-c38-c39-40d3-37d1-38d3I15-39d1-15-45-0125-30-4389-4982-41507-44407.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c37-c38-c39-40d3-37d3S10-38d1S30-39d3S2-45-00156-025-0125-3432-3702-32660-36927.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c40-c37-c38-c39-40d3a-37d3a-38d2a-39d3a-00156-003125-025-0125-6419-8324-66892-67994.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c40-c37-c38-c39-40d4I15-37d1-38d1-39d1-00156-30-30-30-7052-7482-64888-68669.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c37-c39-c38-40d3-37d1-39d3I15-38d3I35-30-30-00625-0125-2954-3070-27107-29794.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c37-c39-c38-40d3-37d3S10-39d3I15-38d1-45-00156-00625-30-3432-3702-27107-30837.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c37-c39-c38-40d3-37d4I35-39d4I35-38d3I15-15-00156-025-0125-4389-4687-40864-41507.csv</t>
+    <t xml:space="preserve">c40-c37-c38-c39-40d3a-37d3a-38d3a-39d3a-00078-00156-0125-00625-3898-5376-27797-33341.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c40-c37-c39-c38-40d3a-37d3a-39d3a-38d2a-003125-00625-025-05-14282-21031-112158-130968.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c40-c41-c42-c43-40d3a-41d3U105-42d3U15-43d3U15-00156-0125-0125-00625-6419-6429-6885-7676.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43</t>
+  </si>
+  <si>
     <t xml:space="preserve">c40-c41-c42-c43-40d3a-41d3a-42d3a-43d3a-00078-00078-00156-00156-3898-4856-5154-5674.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-c42-c43-40d4I22-41d3U105-42d3S2-43d3-003125-025-00625-30-11080-11468-11483-11590.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c42-c41-c43-40d3S10-42d3U60-41d3U15-43d3U105-00078-00313-00313-00313-915-1130-1166-1351.csv</t>
+    <t xml:space="preserve">c40-c42-c43-c41-40d3a-42d3U15-43d3U15-41d3U15-00156-0125-00625-0125-6419-6885-7676-9391.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c40-c42-c43-c41-40d4I22-42d4I22-43d4I15-41d4I15-003125-003125-00625-003125-11080-11953-13918-14945.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c40-c43-c41-c42-40d3S10-43d3U105-41d3U60-42d3-00078-00313-00313-30-915-1351-1448-1583.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c40-c42-c43-41d3U105-40d2-42d3U15-43d3U15-0125-45-0125-00625-6429-6498-6885-7676.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c40-c42-c43-41d4I35-40d4I15-42d3-43d3U15-00156-00156-15-00625-7037-7052-7201-7676.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c42-c43-c40-41d3U60-42d3U60-43d3-40d3-00156-00156-45-45-586-661-702-802.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c41-c43-c40-c42-41d3S30-43d2S10-40d2S10-42d3S2-0125-0125-0125-0125-18653-21611-21763-26116.csv</t>
   </si>
   <si>
@@ -296,9 +263,6 @@
     <t xml:space="preserve">c41-c43-c40-c42-41d4I22-43d4I22-40d4I35-42d4I15-00156-003125-00156-00156-5433-5846-6008-6946.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c41-c43-c42-c40-41d3-43d3S10-42d3U15-40d3-15-00078-00313-30-1913-1934-2006-2172.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c41-c43-c42-c40-41d3S30-43d3S10-42d3S2-40d3S10-00156-00078-00078-00156-1695-1934-2219-2220.csv</t>
   </si>
   <si>
@@ -308,31 +272,25 @@
     <t xml:space="preserve">c42-c40-c41-c43-42d4I15-40d4I15-41d4I15-43d4I22-00156-00156-00156-00625-6946-7052-8052-9713.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c40-c43-c41-42d3U15-40d4I15-43d3U15-41d3U15-0125-00156-00625-0125-6885-7052-7676-9391.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c42-c41-c43-c40-42d3-41d3-43d4I15-40d3-15-45-00156-15-2288-2568-2658-2875.csv</t>
+    <t xml:space="preserve">c42-c41-c43-c40-42d3U60-41d3U15-43d3U105-40d3a-00313-00313-00313-00078-1130-1166-1351-3898.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c42-c41-c43-c40-42d3a-41d3a-43d3a-40d3a-00625-00625-00625-0125-22419-23585-31591-43736.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-c40-c41-42d3U105-43d3U105-40d3-41d3U60-00625-00625-45-00625-3026-3228-3432-3645.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c42-c43-c40-c41-42d3a-43d3a-40d3a-41d3a-00156-00156-00156-00156-5154-5674-6419-7630.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c43-c41-c40-c42-43d3-41d3U105-40d2-42d3U15-30-0125-45-0125-6427-6429-6498-6885.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c43-c41-c42-c40-43d3U105-41d3U60-42d3U15-40d3-00313-00313-00313-30-1351-1448-2006-2172.csv</t>
+    <t xml:space="preserve">c42-c43-c41-c40-42d3U105-43d3U105-41d3U60-40d3a-00625-00625-00625-00078-3026-3228-3645-3898.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43-c41-c42-c40-43d3U105-41d3U60-42d3U15-40d3a-00313-00313-00313-00078-1351-1448-2006-3898.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c43-c41-c42-c40-43d3a-41d3a-42d3a-40d3a-003125-003125-003125-003125-10202-10975-11970-14282.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c43-c42-c40-c41-43d3U105-42d3S2-40d3-41d3S30-00625-00156-45-003125-3228-3242-3432-3611.csv</t>
+    <t xml:space="preserve">c43-c42-c40-c41-43d3a-42d3a-40d3a-41d3a-00078-00078-00078-00078-2722-3084-3898-4856.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c43-c42-c41-c40-43d4I15-42d4I22-41d4I22-40d4I35-00156-00156-00156-00156-2658-4636-5433-6008.csv</t>
@@ -347,7 +305,7 @@
     <t xml:space="preserve">c43-c42-c41-c40-43d4I35-42d4I22-41d4I22-40d4I35-00156-00156-00156-00156-3643-4636-5433-6008.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-c47-c46-44d3-45d3-47d3-46d4I15-30-15-30-003125-1816-2216-2378-8768.csv</t>
+    <t xml:space="preserve">c44-c45-c47-c46-44d3a-45d3a-47d3a-46d3a-003125-003125-003125-0125-10346-13722-13868-48592.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c44</t>
@@ -365,15 +323,15 @@
     <t xml:space="preserve">c44-c45-c47-c46-44d4I35-45d4I15-47d4I22-46d4I15-00156-00156-00156-00625-2947-3102-3908-14456.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c47-c45-c46-44d3S30-47d3-45d3S2-46d4I22-00625-30-00156-0125-4868-5416-5460-20621.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c47-c45-c46-44d3S30-47d3S30-45d3S2-46d3S10-00078-00078-00078-00156-1036-1197-1709-3247.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c45-c44-c47-c46-45d3S2-44d3S30-47d3S30-46d2S10-00078-003125-00156-003125-1709-2662-3040-6522.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c45-c44-c47-c46-45d3a-44d3a-47d3a-46d3a-00078-00078-00078-00156-3180-3347-3912-5843.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c45-c44-c47-c46-45d3a-44d3a-47d3a-46d3a-00078-00078-00078-003125-3180-3347-3912-12014.csv</t>
   </si>
   <si>
@@ -389,39 +347,24 @@
     <t xml:space="preserve">c45-c44-c47-c46-45d4I22-44d4I35-47d4I22-46d4I22-00156-00156-00156-00625-2505-2947-3908-11352.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c45-c47-c44-c46-45d2-47d3-44d4I22-46d2-45-30-00625-15-9507-9588-9748-37443.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c47-c44-c46-45d3-47d3-44d3S30-46d3-15-30-003125-15-2216-2378-2662-9273.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c47-c44-c46-45d3-47d4I22-44d3-46d2S10-15-00156-30-00625-3795-3908-3959-15039.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c45-c47-c44-c46-45d3S2-47d3S30-44d3S30-46d2S10-00156-007-0125-0125-5460-8072-8145-27899.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c45-c47-c44-c46-45d3a-47d3a-44d3a-46d3a-00156-00156-003125-00625-5175-7319-10346-32504.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c45-c47-c44-c46-45d3a-47d3a-44d3a-46d3a-003125-003125-00625-0125-13722-13868-23280-48592.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c45-c47-c44-c46-45d4I22-47d3-44d4I22-46d2-003125-15-003125-30-5717-6033-6170-24204.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c44-c45-c46-47d3S30-44d3-45d3-46d3I35-007-30-30-0125-8072-8314-8847-30064.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c44-c45-c46-47d3S30-44d3S30-45d3S2-46d4I22-00078-00156-00078-003125-1197-1458-1709-5617.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c44-c45-c46-47d3a-44d3a-45d3a-46d2a-00625-0125-0125-025-36901-45891-50820-120690.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c47-c44-c45-c46-47d3a-44d3a-45d3a-46d3a-00156-003125-003125-00625-7319-10346-13722-32504.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c47-c44-c45-c46-47d4I15-44d4I35-45d4I22-46d4I15-00156-003125-003125-0125-4491-4859-5717-22571.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c44-c45-c46-47d4I35-44d3-45d4I35-46d2S10-00156-30-00156-00625-3938-3959-4191-15039.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c44-c45-c46-47d4I35-44d4I22-45d4I22-46d3I35-003125-00625-00625-0125-8836-9748-10173-30064.csv</t>
   </si>
   <si>
@@ -431,31 +374,16 @@
     <t xml:space="preserve">c47-c45-c44-c46-47d2S30-45d2S2-44d3S30-46d1S10-00625-003125-019-025-9172-10768-13907-63568.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d3-45d3S2-44d3-46d2-45-00078-30-45-1697-1709-1816-7099.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d3-45d4I15-44d3S30-46d3I35-15-00625-019-025-11384-13256-13907-57553.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d3-45d4I22-44d4I22-46d4I15-30-003125-003125-0125-5416-5717-6170-22571.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d3-45d4I35-44d2-46d1-15-00625-45-30-11384-12047-12555-51430.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d4I15-45d2-44d4I15-46d3I35-003125-30-003125-0125-6751-7010-7449-30064.csv</t>
+    <t xml:space="preserve">c47-c45-c44-c46-47d3a-45d3a-44d3a-46d3a-00078-00156-00156-003125-3912-5175-5690-12014.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c47-c45-c44-c46-47d4I15-45d4I22-44d4I22-46d4I15-00156-003125-003125-0125-4491-5717-6170-22571.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c45-c44-c46-47d4I35-45d3-44d3-46d2-003125-30-15-15-8836-8847-9435-37443.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c45-c44-c46-47d4I35-45d4I22-44d4I35-46d3I35-003125-00625-00625-025-8836-10173-10225-57553.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c29-c49-c50-48d2d-29d1S30-49d2c-50d3I15-0125-05-025-05-19587-65623-69862-86652.csv</t>
+    <t xml:space="preserve">c48-c29-c49-c50-48d3c-29d2d-49d2d-50d3c-00625-05-0125-025-9455-29622-36100-37518.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c48</t>
@@ -464,9 +392,6 @@
     <t xml:space="preserve">c49</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c29-c49-c50-48d3c-29d2d-49d2d-50d3c-00625-05-0125-025-9455-29622-36100-37518.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c29-c49-c50-48d4I22-29d4I22-49d4I15-50d3I15-00625-0125-025-025-10492-35902-43745-43914.csv</t>
   </si>
   <si>
@@ -476,6 +401,9 @@
     <t xml:space="preserve">c48-c29-c49-c50-48d4a-29d2a-49d3a-50d2a-00156-025-025-025-7889-72765-95649-106577.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c48-c29-c49-c50-48d4a-29d3a-49d4a-50d4a-00078-00625-00156-003125-5468-9973-11722-14364.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c48-c29-c49-c50-48d4e-29d2e-49d3e-50d3c-007-05-025-0125-5931-20402-20503-24073.csv</t>
   </si>
   <si>
@@ -485,54 +413,39 @@
     <t xml:space="preserve">c48-c29-c50-c49-48d3d-29d2d-50d2d-49d2d-00625-05-025-0125-8635-29622-34331-36100.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c29-c50-c49-48d4I15-29d3I35-50d3I22-49d1S10-00625-0125-025-05-13014-45981-50206-51598.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c29-c50-c49-48d4I35-29d4I22-50d4I22-49d4I15-003125-00625-0125-0125-5491-17041-19639-21493.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c48-c29-c50-c49-48d4a-29d3a-50d3a-49d3a-00156-0125-0125-0125-7889-37375-38721-52456.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c48-c29-c50-c49-48d4a-29d3a-50d4a-49d4a-00078-00625-003125-003125-5468-9973-14364-17970.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c48-c29-c50-c49-48d4d-29d2d-50d3e-49d4c-00156-0125-025-009-3507-12550-14225-14373.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c48-c29-c50-c49-48d4e-29d3c-50d4c-49d3e-00078-00625-005-00625-1770-6806-7994-8741.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c29-c50-c49-48d4e-29d4I15-50d2S30-49d3e-00078-00156-025-00625-1770-7181-7818-8741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c48-c49-c29-c50-48d2e-49d2S10-29d2c-50d3c-00625-025-025-00625-4448-16011-17362-17497.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c49-c29-c50-48d4e-49d4c-29d3c-50d3e-00078-003125-00625-00625-1770-6350-6806-6971.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c49-c50-c29-48d3d-49d4I15-50d4I15-29d4I15-003125-00625-00625-003125-3213-12242-12771-13560.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c49-c50-c29-48d4I22-49d4I15-50d3I15-29d3I35-00625-025-025-0125-10492-43745-43914-45981.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c49-c50-c29-48d4I35-49d3I35-50d3I22-29d3I35-0125-05-05-025-22301-84207-89910-92106.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c49-c50-c29-48d4a-49d3a-50d4a-29d2a-00156-0125-016-025-7889-52456-67760-72765.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c48-c49-c50-c29-48d4a-49d4a-50d4a-29d3a-00078-003125-00625-0125-5468-17970-31136-37375.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c50-c29-c49-48d2S2-50d3I35-29d1S30-49d2c-00625-025-05-025-14465-56835-65623-69862.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c48-c50-c29-c49-48d3d-50d2d-29d4I22-49d2d-00625-025-0125-0125-8635-34331-35902-36100.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c48-c50-c29-c49-48d3e-50d4I35-29d3S30-49d3d-003125-00625-015-00625-2837-11374-11973-12210.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c48-c50-c29-c49-48d4I22-50d4I22-29d4I22-49d4I22-00156-00625-003125-00625-3132-9236-9433-10319.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c48-c50-c29-c49-48d4a-50d4a-29d3a-49d4a-00156-00625-0125-00625-7889-31136-37375-47080.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c48-c50-c29-c49-48d4c-50d3d-29d3c-49d3d-00078-00625-0125-00625-2768-10002-11126-12210.csv</t>
   </si>
   <si>
@@ -554,25 +467,22 @@
     <t xml:space="preserve">c48-c50-c49-c29-48d4e-50d2d-49d3c-29d2c-007-0125-0125-05-5931-25159-26442-27715.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c50-c29-c31-c30-50d2d-29d2c-31d1U105-30d2c-0125-05-025-05-25159-27715-29073-40392.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c50-c29-c31-c30-50d4c-29d3d-31d2-30d2d-005-027-15-025-7994-9048-9232-14610.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c50-c31-c29-c30-50d2d-31d1U105-29d2d-30d2c-0125-025-05-05-25159-29073-29622-40392.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c50-c31-c29-c30-50d3d-31d1-29d3c-30d2e-00625-45-0125-05-10002-10979-11126-20451.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c50-c31-c29-c30-50d3e-31d3S10-29d2e-30d2d-025-011-025-05-14225-15824-15935-27775.csv</t>
+    <t xml:space="preserve">c49-c48-c50-c29-49d4a-48d4a-50d4a-29d3a-00078-00078-00156-003125-4732-5468-5823-6928.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c50-c29-c31-c30-50d2d-29d2c-31d3a-30d2c-0125-05-00625-05-25159-27715-29248-40392.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c50-c29-c31-c30-50d3d-29d3c-31d3a-30d2e-00625-0125-003125-05-10002-11126-11425-20451.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c50-c31-c29-c30-50d2d-31d3a-29d2d-30d2c-0125-00625-05-05-25159-29248-29622-40392.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c50-c31-c29-c30-50d4a-31d3a-29d3a-30d3a-00156-00156-003125-00625-5823-6584-6928-14556.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c50-c31-c29-c30-50d4c-31d4I15-29d3c-30d2d-003125-00156-00625-025-6468-6649-6806-14610.csv</t>
+    <t xml:space="preserve">c50-c31-c29-c30-50d4c-31d3a-29d3c-30d2d-003125-00156-00625-025-6468-6584-6806-14610.csv</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1112,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1210,7 +1120,7 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1218,7 +1128,7 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -1226,39 +1136,39 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
         <v>20</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -1266,7 +1176,7 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
@@ -1274,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -1282,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -1290,7 +1200,7 @@
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -1298,7 +1208,7 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
@@ -1306,7 +1216,7 @@
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1314,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
@@ -1322,7 +1232,7 @@
         <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -1330,7 +1240,7 @@
         <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -1338,7 +1248,7 @@
         <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -1346,7 +1256,7 @@
         <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -1354,7 +1264,7 @@
         <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -1362,7 +1272,7 @@
         <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -1370,7 +1280,7 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -1378,7 +1288,7 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -1386,7 +1296,7 @@
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -1394,7 +1304,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -1402,7 +1312,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
@@ -1410,7 +1320,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -1418,7 +1328,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -1426,7 +1336,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -1434,7 +1344,7 @@
         <v>26</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -1442,7 +1352,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
@@ -1450,7 +1360,7 @@
         <v>26</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -1458,7 +1368,7 @@
         <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
@@ -1466,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
@@ -1474,7 +1384,7 @@
         <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -1482,7 +1392,7 @@
         <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -1490,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -1498,7 +1408,7 @@
         <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -1506,7 +1416,7 @@
         <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
@@ -1514,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
@@ -1546,39 +1456,39 @@
         <v>29</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
         <v>31</v>
-      </c>
-      <c r="B85" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="86">
@@ -1586,7 +1496,7 @@
         <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -1594,7 +1504,7 @@
         <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -1602,7 +1512,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
@@ -1610,7 +1520,7 @@
         <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90">
@@ -1618,7 +1528,7 @@
         <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91">
@@ -1626,7 +1536,7 @@
         <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
@@ -1634,7 +1544,7 @@
         <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -1642,7 +1552,7 @@
         <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94">
@@ -1650,7 +1560,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -1658,7 +1568,7 @@
         <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -1666,7 +1576,7 @@
         <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
@@ -1674,7 +1584,7 @@
         <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98">
@@ -1682,7 +1592,7 @@
         <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99">
@@ -1690,7 +1600,7 @@
         <v>35</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -1698,7 +1608,7 @@
         <v>35</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101">
@@ -1706,7 +1616,7 @@
         <v>35</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102">
@@ -1714,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103">
@@ -1722,7 +1632,7 @@
         <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
@@ -1730,7 +1640,7 @@
         <v>36</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
@@ -1738,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
@@ -1746,7 +1656,7 @@
         <v>37</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107">
@@ -1754,7 +1664,7 @@
         <v>37</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108">
@@ -1762,7 +1672,7 @@
         <v>37</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
@@ -1770,7 +1680,7 @@
         <v>37</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
@@ -1778,7 +1688,7 @@
         <v>38</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111">
@@ -1786,7 +1696,7 @@
         <v>38</v>
       </c>
       <c r="B111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -1794,7 +1704,7 @@
         <v>38</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
@@ -1802,7 +1712,7 @@
         <v>38</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -1810,7 +1720,7 @@
         <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115">
@@ -1818,7 +1728,7 @@
         <v>39</v>
       </c>
       <c r="B115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
@@ -1826,7 +1736,7 @@
         <v>39</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
@@ -1834,7 +1744,7 @@
         <v>39</v>
       </c>
       <c r="B117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
@@ -1842,7 +1752,7 @@
         <v>40</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
@@ -1850,7 +1760,7 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
@@ -1858,7 +1768,7 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
@@ -1866,7 +1776,7 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122">
@@ -1874,7 +1784,7 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123">
@@ -1882,7 +1792,7 @@
         <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
@@ -1890,7 +1800,7 @@
         <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125">
@@ -1898,7 +1808,7 @@
         <v>41</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126">
@@ -1906,7 +1816,7 @@
         <v>42</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
@@ -1914,7 +1824,7 @@
         <v>42</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
@@ -1922,7 +1832,7 @@
         <v>42</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
@@ -1930,7 +1840,7 @@
         <v>42</v>
       </c>
       <c r="B129" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130">
@@ -1938,7 +1848,7 @@
         <v>43</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131">
@@ -1946,7 +1856,7 @@
         <v>43</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132">
@@ -1954,7 +1864,7 @@
         <v>43</v>
       </c>
       <c r="B132" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -1962,7 +1872,7 @@
         <v>43</v>
       </c>
       <c r="B133" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
@@ -1970,7 +1880,7 @@
         <v>44</v>
       </c>
       <c r="B134" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135">
@@ -1978,7 +1888,7 @@
         <v>44</v>
       </c>
       <c r="B135" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136">
@@ -1986,7 +1896,7 @@
         <v>44</v>
       </c>
       <c r="B136" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137">
@@ -1994,7 +1904,7 @@
         <v>44</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138">
@@ -2002,7 +1912,7 @@
         <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
@@ -2010,7 +1920,7 @@
         <v>45</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140">
@@ -2018,7 +1928,7 @@
         <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
@@ -2026,7 +1936,7 @@
         <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142">
@@ -2034,7 +1944,7 @@
         <v>46</v>
       </c>
       <c r="B142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
@@ -2042,7 +1952,7 @@
         <v>46</v>
       </c>
       <c r="B143" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144">
@@ -2050,7 +1960,7 @@
         <v>46</v>
       </c>
       <c r="B144" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145">
@@ -2058,7 +1968,7 @@
         <v>46</v>
       </c>
       <c r="B145" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="146">
@@ -2066,7 +1976,7 @@
         <v>47</v>
       </c>
       <c r="B146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147">
@@ -2098,7 +2008,7 @@
         <v>51</v>
       </c>
       <c r="B150" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151">
@@ -2130,7 +2040,7 @@
         <v>52</v>
       </c>
       <c r="B154" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155">
@@ -2162,7 +2072,7 @@
         <v>53</v>
       </c>
       <c r="B158" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159">
@@ -2194,7 +2104,7 @@
         <v>54</v>
       </c>
       <c r="B162" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163">
@@ -2226,7 +2136,7 @@
         <v>55</v>
       </c>
       <c r="B166" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="167">
@@ -2258,7 +2168,7 @@
         <v>56</v>
       </c>
       <c r="B170" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="171">
@@ -2266,7 +2176,7 @@
         <v>56</v>
       </c>
       <c r="B171" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="172">
@@ -2274,7 +2184,7 @@
         <v>56</v>
       </c>
       <c r="B172" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173">
@@ -2282,44 +2192,44 @@
         <v>56</v>
       </c>
       <c r="B173" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B174" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B175" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B176" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B177" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B178" t="s">
         <v>48</v>
@@ -2327,7 +2237,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B179" t="s">
         <v>49</v>
@@ -2335,7 +2245,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B180" t="s">
         <v>50</v>
@@ -2343,10 +2253,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
+        <v>58</v>
+      </c>
+      <c r="B181" t="s">
         <v>59</v>
-      </c>
-      <c r="B181" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="182">
@@ -2378,7 +2288,7 @@
         <v>60</v>
       </c>
       <c r="B185" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="186">
@@ -2386,7 +2296,7 @@
         <v>61</v>
       </c>
       <c r="B186" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="187">
@@ -2394,7 +2304,7 @@
         <v>61</v>
       </c>
       <c r="B187" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="188">
@@ -2402,7 +2312,7 @@
         <v>61</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="189">
@@ -2410,7 +2320,7 @@
         <v>61</v>
       </c>
       <c r="B189" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="190">
@@ -2418,7 +2328,7 @@
         <v>62</v>
       </c>
       <c r="B190" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="191">
@@ -2426,7 +2336,7 @@
         <v>62</v>
       </c>
       <c r="B191" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="192">
@@ -2434,7 +2344,7 @@
         <v>62</v>
       </c>
       <c r="B192" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="193">
@@ -2442,7 +2352,7 @@
         <v>62</v>
       </c>
       <c r="B193" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194">
@@ -2450,7 +2360,7 @@
         <v>63</v>
       </c>
       <c r="B194" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195">
@@ -2482,7 +2392,7 @@
         <v>64</v>
       </c>
       <c r="B198" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="199">
@@ -2514,7 +2424,7 @@
         <v>65</v>
       </c>
       <c r="B202" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="203">
@@ -2546,7 +2456,7 @@
         <v>66</v>
       </c>
       <c r="B206" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="207">
@@ -2578,7 +2488,7 @@
         <v>67</v>
       </c>
       <c r="B210" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211">
@@ -2610,7 +2520,7 @@
         <v>68</v>
       </c>
       <c r="B214" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215">
@@ -2642,7 +2552,7 @@
         <v>69</v>
       </c>
       <c r="B218" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="219">
@@ -2650,7 +2560,7 @@
         <v>69</v>
       </c>
       <c r="B219" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="220">
@@ -2658,7 +2568,7 @@
         <v>69</v>
       </c>
       <c r="B220" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="221">
@@ -2666,7 +2576,7 @@
         <v>69</v>
       </c>
       <c r="B221" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="222">
@@ -2674,7 +2584,7 @@
         <v>70</v>
       </c>
       <c r="B222" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="223">
@@ -2682,7 +2592,7 @@
         <v>70</v>
       </c>
       <c r="B223" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="224">
@@ -2690,7 +2600,7 @@
         <v>70</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="225">
@@ -2698,7 +2608,7 @@
         <v>70</v>
       </c>
       <c r="B225" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="226">
@@ -2730,7 +2640,7 @@
         <v>71</v>
       </c>
       <c r="B229" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="230">
@@ -2738,7 +2648,7 @@
         <v>72</v>
       </c>
       <c r="B230" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="231">
@@ -2746,7 +2656,7 @@
         <v>72</v>
       </c>
       <c r="B231" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="232">
@@ -2754,7 +2664,7 @@
         <v>72</v>
       </c>
       <c r="B232" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="233">
@@ -2762,231 +2672,231 @@
         <v>72</v>
       </c>
       <c r="B233" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B234" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
+        <v>76</v>
+      </c>
+      <c r="B235" t="s">
         <v>73</v>
-      </c>
-      <c r="B235" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B236" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B237" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B238" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B239" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
+        <v>77</v>
+      </c>
+      <c r="B240" t="s">
         <v>74</v>
-      </c>
-      <c r="B240" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B241" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B242" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B243" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B244" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
+        <v>78</v>
+      </c>
+      <c r="B245" t="s">
         <v>75</v>
-      </c>
-      <c r="B245" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B247" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B248" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B249" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B250" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B251" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B252" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B253" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B254" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B255" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B256" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B257" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B258" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B259" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B260" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B261" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262">
@@ -2994,7 +2904,7 @@
         <v>83</v>
       </c>
       <c r="B262" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="263">
@@ -3002,7 +2912,7 @@
         <v>83</v>
       </c>
       <c r="B263" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="264">
@@ -3010,7 +2920,7 @@
         <v>83</v>
       </c>
       <c r="B264" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="265">
@@ -3018,7 +2928,7 @@
         <v>83</v>
       </c>
       <c r="B265" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="266">
@@ -3026,7 +2936,7 @@
         <v>84</v>
       </c>
       <c r="B266" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="267">
@@ -3034,7 +2944,7 @@
         <v>84</v>
       </c>
       <c r="B267" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="268">
@@ -3042,7 +2952,7 @@
         <v>84</v>
       </c>
       <c r="B268" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="269">
@@ -3050,7 +2960,7 @@
         <v>84</v>
       </c>
       <c r="B269" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="270">
@@ -3058,7 +2968,7 @@
         <v>85</v>
       </c>
       <c r="B270" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="271">
@@ -3066,7 +2976,7 @@
         <v>85</v>
       </c>
       <c r="B271" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272">
@@ -3074,7 +2984,7 @@
         <v>85</v>
       </c>
       <c r="B272" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273">
@@ -3082,7 +2992,7 @@
         <v>85</v>
       </c>
       <c r="B273" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274">
@@ -3090,7 +3000,7 @@
         <v>86</v>
       </c>
       <c r="B274" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="275">
@@ -3098,7 +3008,7 @@
         <v>86</v>
       </c>
       <c r="B275" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="276">
@@ -3106,7 +3016,7 @@
         <v>86</v>
       </c>
       <c r="B276" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="277">
@@ -3114,7 +3024,7 @@
         <v>86</v>
       </c>
       <c r="B277" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="278">
@@ -3122,7 +3032,7 @@
         <v>87</v>
       </c>
       <c r="B278" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="279">
@@ -3130,7 +3040,7 @@
         <v>87</v>
       </c>
       <c r="B279" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="280">
@@ -3138,7 +3048,7 @@
         <v>87</v>
       </c>
       <c r="B280" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="281">
@@ -3146,7 +3056,7 @@
         <v>87</v>
       </c>
       <c r="B281" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="282">
@@ -3154,7 +3064,7 @@
         <v>88</v>
       </c>
       <c r="B282" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="283">
@@ -3162,7 +3072,7 @@
         <v>88</v>
       </c>
       <c r="B283" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="284">
@@ -3170,7 +3080,7 @@
         <v>88</v>
       </c>
       <c r="B284" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="285">
@@ -3178,7 +3088,7 @@
         <v>88</v>
       </c>
       <c r="B285" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="286">
@@ -3186,7 +3096,7 @@
         <v>89</v>
       </c>
       <c r="B286" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="287">
@@ -3194,7 +3104,7 @@
         <v>89</v>
       </c>
       <c r="B287" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="288">
@@ -3202,7 +3112,7 @@
         <v>89</v>
       </c>
       <c r="B288" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="289">
@@ -3210,7 +3120,7 @@
         <v>89</v>
       </c>
       <c r="B289" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="290">
@@ -3218,7 +3128,7 @@
         <v>90</v>
       </c>
       <c r="B290" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="291">
@@ -3226,7 +3136,7 @@
         <v>90</v>
       </c>
       <c r="B291" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="292">
@@ -3234,7 +3144,7 @@
         <v>90</v>
       </c>
       <c r="B292" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="293">
@@ -3242,7 +3152,7 @@
         <v>90</v>
       </c>
       <c r="B293" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="294">
@@ -3250,7 +3160,7 @@
         <v>91</v>
       </c>
       <c r="B294" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="295">
@@ -3258,7 +3168,7 @@
         <v>91</v>
       </c>
       <c r="B295" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="296">
@@ -3266,7 +3176,7 @@
         <v>91</v>
       </c>
       <c r="B296" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="297">
@@ -3274,7 +3184,7 @@
         <v>91</v>
       </c>
       <c r="B297" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="298">
@@ -3282,7 +3192,7 @@
         <v>92</v>
       </c>
       <c r="B298" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="299">
@@ -3290,7 +3200,7 @@
         <v>92</v>
       </c>
       <c r="B299" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="300">
@@ -3298,7 +3208,7 @@
         <v>92</v>
       </c>
       <c r="B300" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="301">
@@ -3306,7 +3216,7 @@
         <v>92</v>
       </c>
       <c r="B301" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="302">
@@ -3314,7 +3224,7 @@
         <v>93</v>
       </c>
       <c r="B302" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="303">
@@ -3322,7 +3232,7 @@
         <v>93</v>
       </c>
       <c r="B303" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="304">
@@ -3330,7 +3240,7 @@
         <v>93</v>
       </c>
       <c r="B304" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="305">
@@ -3338,7 +3248,7 @@
         <v>93</v>
       </c>
       <c r="B305" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="306">
@@ -3346,7 +3256,7 @@
         <v>94</v>
       </c>
       <c r="B306" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="307">
@@ -3354,7 +3264,7 @@
         <v>94</v>
       </c>
       <c r="B307" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="308">
@@ -3362,7 +3272,7 @@
         <v>94</v>
       </c>
       <c r="B308" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="309">
@@ -3370,7 +3280,7 @@
         <v>94</v>
       </c>
       <c r="B309" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="310">
@@ -3378,7 +3288,7 @@
         <v>95</v>
       </c>
       <c r="B310" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="311">
@@ -3386,7 +3296,7 @@
         <v>95</v>
       </c>
       <c r="B311" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="312">
@@ -3394,7 +3304,7 @@
         <v>95</v>
       </c>
       <c r="B312" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="313">
@@ -3402,7 +3312,7 @@
         <v>95</v>
       </c>
       <c r="B313" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="314">
@@ -3410,7 +3320,7 @@
         <v>96</v>
       </c>
       <c r="B314" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="315">
@@ -3418,7 +3328,7 @@
         <v>96</v>
       </c>
       <c r="B315" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="316">
@@ -3426,7 +3336,7 @@
         <v>96</v>
       </c>
       <c r="B316" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="317">
@@ -3434,7 +3344,7 @@
         <v>96</v>
       </c>
       <c r="B317" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="318">
@@ -3442,7 +3352,7 @@
         <v>97</v>
       </c>
       <c r="B318" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="319">
@@ -3450,7 +3360,7 @@
         <v>97</v>
       </c>
       <c r="B319" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="320">
@@ -3458,7 +3368,7 @@
         <v>97</v>
       </c>
       <c r="B320" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="321">
@@ -3466,455 +3376,455 @@
         <v>97</v>
       </c>
       <c r="B321" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
+        <v>102</v>
+      </c>
+      <c r="B322" t="s">
         <v>98</v>
-      </c>
-      <c r="B322" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B323" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B324" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B325" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B326" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
+        <v>103</v>
+      </c>
+      <c r="B327" t="s">
         <v>99</v>
-      </c>
-      <c r="B327" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B328" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B329" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B330" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B331" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
+        <v>104</v>
+      </c>
+      <c r="B332" t="s">
         <v>100</v>
-      </c>
-      <c r="B332" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B333" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B334" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B335" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B336" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
+        <v>105</v>
+      </c>
+      <c r="B337" t="s">
         <v>101</v>
-      </c>
-      <c r="B337" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B338" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B339" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B340" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B341" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B342" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B343" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B344" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B345" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B346" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B347" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B348" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B349" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B350" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B351" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B352" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B353" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B354" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B355" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B356" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B357" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B358" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B359" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B360" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B361" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B362" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B363" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B364" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B365" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B366" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B367" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B368" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B369" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B370" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B371" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B372" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B373" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B374" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B375" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B376" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B377" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="378">
@@ -3922,7 +3832,7 @@
         <v>116</v>
       </c>
       <c r="B378" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="379">
@@ -3930,7 +3840,7 @@
         <v>116</v>
       </c>
       <c r="B379" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="380">
@@ -3938,7 +3848,7 @@
         <v>116</v>
       </c>
       <c r="B380" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="381">
@@ -3946,7 +3856,7 @@
         <v>116</v>
       </c>
       <c r="B381" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="382">
@@ -3954,7 +3864,7 @@
         <v>117</v>
       </c>
       <c r="B382" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="383">
@@ -3962,7 +3872,7 @@
         <v>117</v>
       </c>
       <c r="B383" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="384">
@@ -3970,7 +3880,7 @@
         <v>117</v>
       </c>
       <c r="B384" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="385">
@@ -3978,7 +3888,7 @@
         <v>117</v>
       </c>
       <c r="B385" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="386">
@@ -3986,7 +3896,7 @@
         <v>118</v>
       </c>
       <c r="B386" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="387">
@@ -3994,7 +3904,7 @@
         <v>118</v>
       </c>
       <c r="B387" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="388">
@@ -4002,7 +3912,7 @@
         <v>118</v>
       </c>
       <c r="B388" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="389">
@@ -4010,7 +3920,7 @@
         <v>118</v>
       </c>
       <c r="B389" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="390">
@@ -4018,7 +3928,7 @@
         <v>119</v>
       </c>
       <c r="B390" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="391">
@@ -4026,7 +3936,7 @@
         <v>119</v>
       </c>
       <c r="B391" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="392">
@@ -4034,7 +3944,7 @@
         <v>119</v>
       </c>
       <c r="B392" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="393">
@@ -4042,7 +3952,7 @@
         <v>119</v>
       </c>
       <c r="B393" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="394">
@@ -4050,7 +3960,7 @@
         <v>120</v>
       </c>
       <c r="B394" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="395">
@@ -4058,7 +3968,7 @@
         <v>120</v>
       </c>
       <c r="B395" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="396">
@@ -4066,7 +3976,7 @@
         <v>120</v>
       </c>
       <c r="B396" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="397">
@@ -4074,7 +3984,7 @@
         <v>120</v>
       </c>
       <c r="B397" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="398">
@@ -4082,7 +3992,7 @@
         <v>121</v>
       </c>
       <c r="B398" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="399">
@@ -4090,7 +4000,7 @@
         <v>121</v>
       </c>
       <c r="B399" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="400">
@@ -4098,7 +4008,7 @@
         <v>121</v>
       </c>
       <c r="B400" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401">
@@ -4106,7 +4016,7 @@
         <v>121</v>
       </c>
       <c r="B401" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="402">
@@ -4114,7 +4024,7 @@
         <v>122</v>
       </c>
       <c r="B402" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="403">
@@ -4122,7 +4032,7 @@
         <v>122</v>
       </c>
       <c r="B403" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="404">
@@ -4130,7 +4040,7 @@
         <v>122</v>
       </c>
       <c r="B404" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="405">
@@ -4138,7 +4048,7 @@
         <v>122</v>
       </c>
       <c r="B405" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="406">
@@ -4146,7 +4056,7 @@
         <v>123</v>
       </c>
       <c r="B406" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -4154,7 +4064,7 @@
         <v>123</v>
       </c>
       <c r="B407" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="408">
@@ -4162,7 +4072,7 @@
         <v>123</v>
       </c>
       <c r="B408" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="409">
@@ -4170,748 +4080,748 @@
         <v>123</v>
       </c>
       <c r="B409" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B410" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
+        <v>126</v>
+      </c>
+      <c r="B411" t="s">
         <v>124</v>
-      </c>
-      <c r="B411" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B412" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B413" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B414" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B415" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
+        <v>127</v>
+      </c>
+      <c r="B416" t="s">
         <v>125</v>
-      </c>
-      <c r="B416" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B417" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B418" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B419" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B420" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B421" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B422" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B423" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B424" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B425" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B426" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B427" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B428" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B429" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B430" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B431" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B432" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B433" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B434" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B435" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B436" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B437" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B438" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B439" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B440" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B441" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B442" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B443" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B444" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B445" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B446" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B447" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B448" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B449" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B450" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B451" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B452" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B453" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B454" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B455" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B456" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B457" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B458" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B459" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B460" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B461" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B462" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B463" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B464" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B465" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B466" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B467" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B468" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B469" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B470" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B471" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B472" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B473" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B474" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B475" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B476" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B477" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B478" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B479" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B480" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B481" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B482" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B483" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B484" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B485" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B486" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B487" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B488" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B489" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B490" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B491" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B492" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B493" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B494" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B495" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B496" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B497" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B498" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B499" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B500" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B501" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B502" t="s">
         <v>3</v>
@@ -4919,23 +4829,23 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B503" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B504" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B505" t="s">
         <v>6</v>
@@ -4954,7 +4864,7 @@
         <v>150</v>
       </c>
       <c r="B507" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="508">
@@ -4962,7 +4872,7 @@
         <v>150</v>
       </c>
       <c r="B508" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="509">
@@ -4986,7 +4896,7 @@
         <v>151</v>
       </c>
       <c r="B511" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="512">
@@ -4994,7 +4904,7 @@
         <v>151</v>
       </c>
       <c r="B512" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="513">
@@ -5018,7 +4928,7 @@
         <v>152</v>
       </c>
       <c r="B515" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="516">
@@ -5026,7 +4936,7 @@
         <v>152</v>
       </c>
       <c r="B516" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
@@ -5050,7 +4960,7 @@
         <v>153</v>
       </c>
       <c r="B519" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="520">
@@ -5058,7 +4968,7 @@
         <v>153</v>
       </c>
       <c r="B520" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521">
@@ -5082,7 +4992,7 @@
         <v>154</v>
       </c>
       <c r="B523" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="524">
@@ -5090,7 +5000,7 @@
         <v>154</v>
       </c>
       <c r="B524" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -5114,7 +5024,7 @@
         <v>155</v>
       </c>
       <c r="B527" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="528">
@@ -5122,7 +5032,7 @@
         <v>155</v>
       </c>
       <c r="B528" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
@@ -5146,7 +5056,7 @@
         <v>156</v>
       </c>
       <c r="B531" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="532">
@@ -5154,7 +5064,7 @@
         <v>156</v>
       </c>
       <c r="B532" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="533">
@@ -5162,966 +5072,6 @@
         <v>156</v>
       </c>
       <c r="B533" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="s">
-        <v>157</v>
-      </c>
-      <c r="B534" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="s">
-        <v>157</v>
-      </c>
-      <c r="B535" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="s">
-        <v>157</v>
-      </c>
-      <c r="B536" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="s">
-        <v>157</v>
-      </c>
-      <c r="B537" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="s">
-        <v>158</v>
-      </c>
-      <c r="B538" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="s">
-        <v>158</v>
-      </c>
-      <c r="B539" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="s">
-        <v>158</v>
-      </c>
-      <c r="B540" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="s">
-        <v>158</v>
-      </c>
-      <c r="B541" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="s">
-        <v>159</v>
-      </c>
-      <c r="B542" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="s">
-        <v>159</v>
-      </c>
-      <c r="B543" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="s">
-        <v>159</v>
-      </c>
-      <c r="B544" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="s">
-        <v>159</v>
-      </c>
-      <c r="B545" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="s">
-        <v>160</v>
-      </c>
-      <c r="B546" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="s">
-        <v>160</v>
-      </c>
-      <c r="B547" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="s">
-        <v>160</v>
-      </c>
-      <c r="B548" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="s">
-        <v>160</v>
-      </c>
-      <c r="B549" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="s">
-        <v>161</v>
-      </c>
-      <c r="B550" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="s">
-        <v>161</v>
-      </c>
-      <c r="B551" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="s">
-        <v>161</v>
-      </c>
-      <c r="B552" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="s">
-        <v>161</v>
-      </c>
-      <c r="B553" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="s">
-        <v>162</v>
-      </c>
-      <c r="B554" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="s">
-        <v>162</v>
-      </c>
-      <c r="B555" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="s">
-        <v>162</v>
-      </c>
-      <c r="B556" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="s">
-        <v>162</v>
-      </c>
-      <c r="B557" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="s">
-        <v>163</v>
-      </c>
-      <c r="B558" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="s">
-        <v>163</v>
-      </c>
-      <c r="B559" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="s">
-        <v>163</v>
-      </c>
-      <c r="B560" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="s">
-        <v>163</v>
-      </c>
-      <c r="B561" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="s">
-        <v>164</v>
-      </c>
-      <c r="B562" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="s">
-        <v>164</v>
-      </c>
-      <c r="B563" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="s">
-        <v>164</v>
-      </c>
-      <c r="B564" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="s">
-        <v>164</v>
-      </c>
-      <c r="B565" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="s">
-        <v>165</v>
-      </c>
-      <c r="B566" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="s">
-        <v>165</v>
-      </c>
-      <c r="B567" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="s">
-        <v>165</v>
-      </c>
-      <c r="B568" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="s">
-        <v>165</v>
-      </c>
-      <c r="B569" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="s">
-        <v>166</v>
-      </c>
-      <c r="B570" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="s">
-        <v>166</v>
-      </c>
-      <c r="B571" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="s">
-        <v>166</v>
-      </c>
-      <c r="B572" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="s">
-        <v>166</v>
-      </c>
-      <c r="B573" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="s">
-        <v>167</v>
-      </c>
-      <c r="B574" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="s">
-        <v>167</v>
-      </c>
-      <c r="B575" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="s">
-        <v>167</v>
-      </c>
-      <c r="B576" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="s">
-        <v>167</v>
-      </c>
-      <c r="B577" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="s">
-        <v>168</v>
-      </c>
-      <c r="B578" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="s">
-        <v>168</v>
-      </c>
-      <c r="B579" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="s">
-        <v>168</v>
-      </c>
-      <c r="B580" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="s">
-        <v>168</v>
-      </c>
-      <c r="B581" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="s">
-        <v>169</v>
-      </c>
-      <c r="B582" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="s">
-        <v>169</v>
-      </c>
-      <c r="B583" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="s">
-        <v>169</v>
-      </c>
-      <c r="B584" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="s">
-        <v>169</v>
-      </c>
-      <c r="B585" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="s">
-        <v>170</v>
-      </c>
-      <c r="B586" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="s">
-        <v>170</v>
-      </c>
-      <c r="B587" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="s">
-        <v>170</v>
-      </c>
-      <c r="B588" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="s">
-        <v>170</v>
-      </c>
-      <c r="B589" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="s">
-        <v>171</v>
-      </c>
-      <c r="B590" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="s">
-        <v>171</v>
-      </c>
-      <c r="B591" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="s">
-        <v>171</v>
-      </c>
-      <c r="B592" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="s">
-        <v>171</v>
-      </c>
-      <c r="B593" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="s">
-        <v>172</v>
-      </c>
-      <c r="B594" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="s">
-        <v>172</v>
-      </c>
-      <c r="B595" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="s">
-        <v>172</v>
-      </c>
-      <c r="B596" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="s">
-        <v>172</v>
-      </c>
-      <c r="B597" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="s">
-        <v>173</v>
-      </c>
-      <c r="B598" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="s">
-        <v>173</v>
-      </c>
-      <c r="B599" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="s">
-        <v>173</v>
-      </c>
-      <c r="B600" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="s">
-        <v>173</v>
-      </c>
-      <c r="B601" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="s">
-        <v>174</v>
-      </c>
-      <c r="B602" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="s">
-        <v>174</v>
-      </c>
-      <c r="B603" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="s">
-        <v>174</v>
-      </c>
-      <c r="B604" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="s">
-        <v>174</v>
-      </c>
-      <c r="B605" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="s">
-        <v>175</v>
-      </c>
-      <c r="B606" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="s">
-        <v>175</v>
-      </c>
-      <c r="B607" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="s">
-        <v>175</v>
-      </c>
-      <c r="B608" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="s">
-        <v>175</v>
-      </c>
-      <c r="B609" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="s">
-        <v>176</v>
-      </c>
-      <c r="B610" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="s">
-        <v>176</v>
-      </c>
-      <c r="B611" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="s">
-        <v>176</v>
-      </c>
-      <c r="B612" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="s">
-        <v>176</v>
-      </c>
-      <c r="B613" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="s">
-        <v>177</v>
-      </c>
-      <c r="B614" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="s">
-        <v>177</v>
-      </c>
-      <c r="B615" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="s">
-        <v>177</v>
-      </c>
-      <c r="B616" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="s">
-        <v>177</v>
-      </c>
-      <c r="B617" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="s">
-        <v>178</v>
-      </c>
-      <c r="B618" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="s">
-        <v>178</v>
-      </c>
-      <c r="B619" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="s">
-        <v>178</v>
-      </c>
-      <c r="B620" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="s">
-        <v>178</v>
-      </c>
-      <c r="B621" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="s">
-        <v>179</v>
-      </c>
-      <c r="B622" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="s">
-        <v>179</v>
-      </c>
-      <c r="B623" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="s">
-        <v>179</v>
-      </c>
-      <c r="B624" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="s">
-        <v>179</v>
-      </c>
-      <c r="B625" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="s">
-        <v>180</v>
-      </c>
-      <c r="B626" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="s">
-        <v>180</v>
-      </c>
-      <c r="B627" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="s">
-        <v>180</v>
-      </c>
-      <c r="B628" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="s">
-        <v>180</v>
-      </c>
-      <c r="B629" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="s">
-        <v>181</v>
-      </c>
-      <c r="B630" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="s">
-        <v>181</v>
-      </c>
-      <c r="B631" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="s">
-        <v>181</v>
-      </c>
-      <c r="B632" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="s">
-        <v>181</v>
-      </c>
-      <c r="B633" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="s">
-        <v>182</v>
-      </c>
-      <c r="B634" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="s">
-        <v>182</v>
-      </c>
-      <c r="B635" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="s">
-        <v>182</v>
-      </c>
-      <c r="B636" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="s">
-        <v>182</v>
-      </c>
-      <c r="B637" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="s">
-        <v>183</v>
-      </c>
-      <c r="B638" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="s">
-        <v>183</v>
-      </c>
-      <c r="B639" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="s">
-        <v>183</v>
-      </c>
-      <c r="B640" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="s">
-        <v>183</v>
-      </c>
-      <c r="B641" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="s">
-        <v>184</v>
-      </c>
-      <c r="B642" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="s">
-        <v>184</v>
-      </c>
-      <c r="B643" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="s">
-        <v>184</v>
-      </c>
-      <c r="B644" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="s">
-        <v>184</v>
-      </c>
-      <c r="B645" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="s">
-        <v>185</v>
-      </c>
-      <c r="B646" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="s">
-        <v>185</v>
-      </c>
-      <c r="B647" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="s">
-        <v>185</v>
-      </c>
-      <c r="B648" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="s">
-        <v>185</v>
-      </c>
-      <c r="B649" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="s">
-        <v>186</v>
-      </c>
-      <c r="B650" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="s">
-        <v>186</v>
-      </c>
-      <c r="B651" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="s">
-        <v>186</v>
-      </c>
-      <c r="B652" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="s">
-        <v>186</v>
-      </c>
-      <c r="B653" t="s">
         <v>6</v>
       </c>
     </row>
